--- a/src/test/resources/testdata/block_reg.xlsx
+++ b/src/test/resources/testdata/block_reg.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dr6/Code/stan/core/src/test/resources/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59177633-906C-AB42-8FD2-CE6F6D5BCB09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1607B84-E4BC-FD4C-9C1F-7F427D261264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="760" windowWidth="27640" windowHeight="15900" activeTab="2" xr2:uid="{5C25E200-6C46-9D45-98E6-7DE84B4E9124}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
   <si>
     <t>DONOR INFO</t>
   </si>
@@ -190,6 +190,24 @@
   </si>
   <si>
     <t>Homo sapiens (Human)</t>
+  </si>
+  <si>
+    <t>Slot address</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>External barcode</t>
+  </si>
+  <si>
+    <t>XBC1</t>
+  </si>
+  <si>
+    <t>XBC2</t>
+  </si>
+  <si>
+    <t>XBC3</t>
   </si>
 </sst>
 </file>
@@ -559,7 +577,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E192D199-3D24-FD46-8181-D5EE66C2F681}">
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
@@ -575,14 +593,16 @@
     <col min="11" max="11" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="41" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="41.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="59.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="31" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="41.1640625" customWidth="1"/>
+    <col min="15" max="15" width="59.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.5" customWidth="1"/>
+    <col min="17" max="17" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="31" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="33.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
         <v>0</v>
       </c>
@@ -592,11 +612,11 @@
       <c r="K1" t="s">
         <v>2</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -637,22 +657,28 @@
         <v>14</v>
       </c>
       <c r="N2" t="s">
+        <v>50</v>
+      </c>
+      <c r="O2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q2" t="s">
         <v>16</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>18</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -692,20 +718,26 @@
       <c r="M3">
         <v>1</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3">
         <v>19</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q3" t="s">
         <v>27</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="S3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>35</v>
       </c>
@@ -739,20 +771,26 @@
       <c r="M4">
         <v>1</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4">
         <v>19</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q4" t="s">
         <v>27</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="S4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>36</v>
       </c>
@@ -789,19 +827,25 @@
       <c r="M5">
         <v>2</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="s">
+        <v>51</v>
+      </c>
+      <c r="O5">
         <v>21</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" t="s">
         <v>27</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" t="s">
         <v>41</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="S5" t="s">
         <v>39</v>
       </c>
-      <c r="R5" t="s">
+      <c r="T5" t="s">
         <v>40</v>
       </c>
     </row>
